--- a/data/references/Kookboek.xlsx
+++ b/data/references/Kookboek.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bert_vanhecke\Documents\Soortenbehoud\Turnhouts Vennegebied\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bert_vanhecke\Documents\Soortenbehoud\arpl\data\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
   <si>
     <t>Techniek / GIS-laag</t>
   </si>
@@ -701,6 +701,32 @@
       </rPr>
       <t xml:space="preserve"> interactie.</t>
     </r>
+  </si>
+  <si>
+    <t>gladdeslang</t>
+  </si>
+  <si>
+    <t>Randen toevoegen</t>
+  </si>
+  <si>
+    <t>cellDistanceLe(gladdeslang_biotoop2, 50, meter))</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nieuw: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Voegt enkel de randen toe binnen de 50 m ipv heel de cluster)</t>
+    </r>
+  </si>
+  <si>
+    <t>terra::buffer en terra::ifel</t>
   </si>
 </sst>
 </file>
@@ -757,7 +783,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -780,11 +806,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -796,6 +833,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1078,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
@@ -1358,6 +1401,23 @@
         <v>72</v>
       </c>
     </row>
+    <row r="17" spans="1:5" ht="41.4">
+      <c r="A17" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
